--- a/data/scenarios/food_as_tech.xlsx
+++ b/data/scenarios/food_as_tech.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18360" windowHeight="6615" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18360" windowHeight="6615" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Regions" sheetId="7" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="268">
   <si>
     <t>f_food</t>
   </si>
@@ -830,6 +830,9 @@
   </si>
   <si>
     <t>Biofuel, ethanol straw</t>
+  </si>
+  <si>
+    <t>&lt;-- Unfeasibility problems if this does not reach zero by 2040</t>
   </si>
 </sst>
 </file>
@@ -839,7 +842,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -927,6 +930,13 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1052,7 +1062,7 @@
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1100,6 +1110,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1207,7 +1218,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="sv-SE"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -1349,7 +1360,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="531027119"/>
@@ -1391,7 +1402,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="531029615"/>
@@ -1433,7 +1444,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="sv-SE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1532,7 +1543,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="sv-SE"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -1674,7 +1685,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="531027119"/>
@@ -1718,7 +1729,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="531029615"/>
@@ -1760,7 +1771,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="sv-SE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -10278,7 +10289,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -10290,7 +10301,7 @@
     <col min="7" max="13" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -10331,7 +10342,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>98</v>
       </c>
@@ -10353,7 +10364,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -10373,7 +10384,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>98</v>
       </c>
@@ -10393,7 +10404,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>123</v>
       </c>
@@ -10413,7 +10424,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -10433,7 +10444,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>98</v>
       </c>
@@ -10453,7 +10464,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>123</v>
       </c>
@@ -10473,7 +10484,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
         <v>181</v>
       </c>
@@ -10483,11 +10494,17 @@
       <c r="G12" s="31">
         <v>1</v>
       </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
       <c r="M12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N12" s="47" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
         <v>182</v>
       </c>
@@ -10496,6 +10513,9 @@
       </c>
       <c r="G13" s="31">
         <v>1</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
       </c>
       <c r="M13">
         <v>0</v>
